--- a/Firmware/Modules/Diag/Diag_State_Machine.xlsx
+++ b/Firmware/Modules/Diag/Diag_State_Machine.xlsx
@@ -55,7 +55,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -94,17 +94,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -161,12 +151,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -531,7 +515,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -688,16 +672,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -731,22 +715,22 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>خاموش/Init</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>پس از ریست برد</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>خواندن فلش و انتخاب رکورد سالم</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>آپتایم صفر، شمارنده‌ها از فلش</t>
         </is>
@@ -797,66 +781,66 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>قطع برق</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>input_present 1→0</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>بازگشت برق 0→1</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>زمان قطع ثبت، پس از وصل مدت محاسبه</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>ذخیره دیبانس</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>تغییر داده + 60ثانیه</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>نوشتن روی صفحه دیگر</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>ping-pong با CRC32</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>همگام ساعت</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>دریافت TIME_SYNC از ESP</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>boardTimeBase = unix - uptime</t>
         </is>
@@ -873,17 +857,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -982,66 +966,66 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>چانک 0</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>DIAG_DATA</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>آمار پایه 7×u32</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>ارسال از ESP-Link</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>چانک 1/2</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>DIAG_DATA</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>خطاها 5تایی هر کدام 8×u32</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>timestamp/faultMask/vIn/vPack/vLow/vHigh/state1/state2</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>چانک 3/4</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>DIAG_DATA</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>قطع/وصل 10تایی هر کدام 3×u32</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>off/on/duration</t>
         </is>

--- a/Firmware/Modules/Diag/Diag_State_Machine.xlsx
+++ b/Firmware/Modules/Diag/Diag_State_Machine.xlsx
@@ -676,7 +676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -754,7 +754,7 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>شمارنده شارژ و آپتایم فعال</t>
+          <t>شمارنده شارژ و آپتایم فعال (آپتایم از تیک کرنل)</t>
         </is>
       </c>
     </row>
@@ -827,20 +827,42 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>ذخیره حین شارژ</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>شارژ پیوسته + 600ثانیه (DIAG_SAVE_CHARGE_SEC)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>نوشتن روی صفحه دیگر، شارژ ادامه دارد</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>قطع برق وسط شارژ حداکثر 10 دقیقه داده از دست می‌دهد</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>همگام ساعت</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>دریافت TIME_SYNC از ESP</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>boardTimeBase = unix - uptime</t>
         </is>

--- a/Firmware/Modules/Diag/Diag_State_Machine.xlsx
+++ b/Firmware/Modules/Diag/Diag_State_Machine.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1 حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2 فلش" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 حالت‌ها" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 فلش" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
